--- a/重点商品CA別進捗_2026年9月.xlsx
+++ b/重点商品CA別進捗_2026年9月.xlsx
@@ -940,7 +940,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="2">
                 <v>1</v>
@@ -1780,7 +1780,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="2">
                 <v>4</v>
@@ -2458,7 +2458,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>4</v>
+                <v>6</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -2519,7 +2519,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="4"/>
+          <max val="6"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -2620,7 +2620,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>3</v>
+                <v>5</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -2681,7 +2681,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="5"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -2944,7 +2944,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>3</v>
+                <v>5</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -3005,7 +3005,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="5"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -3106,7 +3106,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>2</v>
+                <v>4</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -3268,7 +3268,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>4</v>
+                <v>6</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -3430,7 +3430,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -3598,10 +3598,10 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="3">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -4096,7 +4096,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -4402,7 +4402,7 @@
             <numLit>
               <ptCount val="4"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -5620,7 +5620,7 @@
                 <v>1</v>
               </pt>
               <pt idx="1">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="2">
                 <v>2</v>
@@ -5641,7 +5641,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>1</v>
+                <v>2</v>
               </pt>
             </numLit>
           </val>
@@ -6364,7 +6364,7 @@
                 <v>5</v>
               </pt>
               <pt idx="1">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -6652,7 +6652,7 @@
                 <v>3</v>
               </pt>
               <pt idx="1">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -6796,7 +6796,7 @@
                 <v>2</v>
               </pt>
               <pt idx="1">
-                <v>4</v>
+                <v>5</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -6845,7 +6845,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="4"/>
+          <max val="5"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6940,7 +6940,7 @@
                 <v>8</v>
               </pt>
               <pt idx="1">
-                <v>7</v>
+                <v>8</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -7249,7 +7249,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>8</v>
+                <v>10</v>
               </pt>
               <pt idx="3">
                 <v>4</v>
@@ -7313,7 +7313,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="8"/>
+          <max val="10"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8869,7 +8869,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>5</v>
+                <v>6</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -9619,7 +9619,7 @@
                 <v>0</v>
               </pt>
               <pt idx="4">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -10840,10 +10840,10 @@
                 <v>1</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
-                <v>5</v>
+                <v>9</v>
               </pt>
               <pt idx="3">
                 <v>3</v>
@@ -10907,7 +10907,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="5"/>
+          <max val="9"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -13197,7 +13197,7 @@
         <v>1</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>2</v>
@@ -13218,7 +13218,7 @@
         <v>0</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
@@ -13234,7 +13234,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L8" s="4" t="n">
         <v>4</v>
@@ -13268,7 +13268,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L9" s="4" t="n">
         <v>0</v>
@@ -13333,10 +13333,10 @@
         <v>1</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>3</v>
@@ -13591,7 +13591,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>1</v>
@@ -13731,7 +13731,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>4</v>
@@ -13904,7 +13904,7 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>1</v>
@@ -13929,7 +13929,7 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>1</v>
@@ -13979,7 +13979,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>1</v>
@@ -14004,7 +14004,7 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>1</v>
@@ -14029,7 +14029,7 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>1</v>
@@ -14054,7 +14054,7 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>0</v>
@@ -14085,10 +14085,10 @@
         <v>0</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>0</v>
@@ -14129,7 +14129,7 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>0</v>
@@ -14249,7 +14249,7 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>1</v>
@@ -14537,7 +14537,7 @@
         <v>5</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>0</v>
@@ -14569,7 +14569,7 @@
         <v>3</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>0</v>
@@ -14585,7 +14585,7 @@
         <v>2</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>0</v>
@@ -14601,7 +14601,7 @@
         <v>8</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>0</v>
@@ -15034,7 +15034,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">

--- a/重点商品CA別進捗_2026年9月.xlsx
+++ b/重点商品CA別進捗_2026年9月.xlsx
@@ -613,7 +613,7 @@
                 <v>0</v>
               </pt>
               <pt idx="4">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="5">
                 <v>0</v>
@@ -665,7 +665,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -787,7 +787,7 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -1114,7 +1114,7 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="4">
                 <v>1</v>
@@ -1123,7 +1123,7 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -1291,7 +1291,7 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
+                <v>2</v>
               </pt>
             </numLit>
           </val>
@@ -1450,7 +1450,7 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -1459,7 +1459,7 @@
                 <v>1</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -1786,7 +1786,7 @@
                 <v>4</v>
               </pt>
               <pt idx="3">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -4705,7 +4705,7 @@
                 <v>3</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -5005,7 +5005,7 @@
                 <v>2</v>
               </pt>
               <pt idx="1">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -5302,7 +5302,7 @@
             <numLit>
               <ptCount val="4"/>
               <pt idx="0">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -5357,7 +5357,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="4"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -5617,7 +5617,7 @@
             <numLit>
               <ptCount val="9"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>2</v>
@@ -6361,7 +6361,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>5</v>
+                <v>6</v>
               </pt>
               <pt idx="1">
                 <v>3</v>
@@ -6413,7 +6413,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="5"/>
+          <max val="6"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6793,7 +6793,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="1">
                 <v>5</v>
@@ -6937,7 +6937,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>8</v>
+                <v>9</v>
               </pt>
               <pt idx="1">
                 <v>8</v>
@@ -6989,7 +6989,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="8"/>
+          <max val="9"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7258,7 +7258,7 @@
                 <v>1</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="6">
                 <v>0</v>
@@ -7405,7 +7405,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -8701,7 +8701,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -8878,10 +8878,10 @@
                 <v>1</v>
               </pt>
               <pt idx="5">
+                <v>2</v>
+              </pt>
+              <pt idx="6">
                 <v>1</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
               </pt>
               <pt idx="7">
                 <v>0</v>
@@ -10837,13 +10837,13 @@
             <numLit>
               <ptCount val="9"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="2">
-                <v>9</v>
+                <v>10</v>
               </pt>
               <pt idx="3">
                 <v>3</v>
@@ -10858,7 +10858,7 @@
                 <v>2</v>
               </pt>
               <pt idx="7">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="8">
                 <v>3</v>
@@ -10907,7 +10907,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="9"/>
+          <max val="10"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -13194,7 +13194,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>2</v>
@@ -13243,7 +13243,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" s="4" t="n">
         <v>0</v>
@@ -13277,10 +13277,10 @@
         <v>1</v>
       </c>
       <c r="N9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="P9" s="4" t="n">
         <v>0</v>
@@ -13330,13 +13330,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>3</v>
@@ -13351,7 +13351,7 @@
         <v>2</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" s="4" t="n">
         <v>3</v>
@@ -13544,7 +13544,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N4" s="4" t="n">
         <v>0</v>
@@ -13578,7 +13578,7 @@
         <v>0</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
@@ -13625,7 +13625,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M7" s="4" t="n">
         <v>1</v>
@@ -13634,7 +13634,7 @@
         <v>0</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
@@ -13662,7 +13662,7 @@
         <v>0</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -13681,7 +13681,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" s="4" t="n">
         <v>0</v>
@@ -13690,7 +13690,7 @@
         <v>1</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -13737,7 +13737,7 @@
         <v>4</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>0</v>
@@ -14290,7 +14290,7 @@
         <v>3</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>0</v>
@@ -14328,7 +14328,7 @@
         <v>2</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>0</v>
@@ -14363,7 +14363,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>0</v>
@@ -14534,7 +14534,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>3</v>
@@ -14582,7 +14582,7 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>5</v>
@@ -14598,7 +14598,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>8</v>
@@ -14630,7 +14630,7 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>0</v>
@@ -14840,7 +14840,7 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>0</v>

--- a/重点商品CA別進捗_2026年9月.xlsx
+++ b/重点商品CA別進捗_2026年9月.xlsx
@@ -616,7 +616,7 @@
                 <v>2</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="6">
                 <v>0</v>
@@ -952,7 +952,7 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="6">
                 <v>0</v>
@@ -1111,7 +1111,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="3">
                 <v>2</v>
@@ -1279,7 +1279,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="3">
                 <v>1</v>
@@ -1795,7 +1795,7 @@
                 <v>2</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -2143,7 +2143,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -4711,7 +4711,7 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -7243,7 +7243,7 @@
             <numLit>
               <ptCount val="9"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -7696,7 +7696,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -7745,7 +7745,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8413,7 +8413,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>0</v>
+                <v>3</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -8465,7 +8465,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8704,7 +8704,7 @@
                 <v>1</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -8863,7 +8863,7 @@
             <numLit>
               <ptCount val="9"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -9028,7 +9028,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -9144,7 +9144,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="5"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>鈴木　聡</v>
               </pt>
@@ -9159,12 +9159,15 @@
               </pt>
               <pt idx="4">
                 <v>石澤　直道</v>
+              </pt>
+              <pt idx="5">
+                <v>伊勢　浩治</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="5"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -9178,6 +9181,9 @@
                 <v>0</v>
               </pt>
               <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
                 <v>0</v>
               </pt>
             </numLit>
@@ -9291,7 +9297,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="5"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>鈴木　聡</v>
               </pt>
@@ -9306,12 +9312,15 @@
               </pt>
               <pt idx="4">
                 <v>石澤　直道</v>
+              </pt>
+              <pt idx="5">
+                <v>伊勢　浩治</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="5"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -9325,6 +9334,9 @@
                 <v>0</v>
               </pt>
               <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
                 <v>0</v>
               </pt>
             </numLit>
@@ -9438,7 +9450,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="5"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>鈴木　聡</v>
               </pt>
@@ -9453,12 +9465,15 @@
               </pt>
               <pt idx="4">
                 <v>石澤　直道</v>
+              </pt>
+              <pt idx="5">
+                <v>伊勢　浩治</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="5"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -9472,6 +9487,9 @@
                 <v>0</v>
               </pt>
               <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
                 <v>0</v>
               </pt>
             </numLit>
@@ -9585,7 +9603,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="5"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>鈴木　聡</v>
               </pt>
@@ -9600,12 +9618,15 @@
               </pt>
               <pt idx="4">
                 <v>石澤　直道</v>
+              </pt>
+              <pt idx="5">
+                <v>伊勢　浩治</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="5"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -9620,6 +9641,9 @@
               </pt>
               <pt idx="4">
                 <v>1</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -9732,7 +9756,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="5"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>鈴木　聡</v>
               </pt>
@@ -9747,12 +9771,15 @@
               </pt>
               <pt idx="4">
                 <v>石澤　直道</v>
+              </pt>
+              <pt idx="5">
+                <v>伊勢　浩治</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="5"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
@@ -9766,6 +9793,9 @@
                 <v>0</v>
               </pt>
               <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
                 <v>0</v>
               </pt>
             </numLit>
@@ -9879,7 +9909,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="5"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>鈴木　聡</v>
               </pt>
@@ -9894,12 +9924,15 @@
               </pt>
               <pt idx="4">
                 <v>石澤　直道</v>
+              </pt>
+              <pt idx="5">
+                <v>伊勢　浩治</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="5"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -9913,6 +9946,9 @@
                 <v>0</v>
               </pt>
               <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
                 <v>0</v>
               </pt>
             </numLit>
@@ -10026,7 +10062,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="5"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>鈴木　聡</v>
               </pt>
@@ -10041,12 +10077,15 @@
               </pt>
               <pt idx="4">
                 <v>石澤　直道</v>
+              </pt>
+              <pt idx="5">
+                <v>伊勢　浩治</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="5"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -10060,6 +10099,9 @@
                 <v>0</v>
               </pt>
               <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
                 <v>0</v>
               </pt>
             </numLit>
@@ -10173,7 +10215,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="5"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>鈴木　聡</v>
               </pt>
@@ -10188,12 +10230,15 @@
               </pt>
               <pt idx="4">
                 <v>石澤　直道</v>
+              </pt>
+              <pt idx="5">
+                <v>伊勢　浩治</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="5"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -10204,10 +10249,13 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="4">
                 <v>1</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -10320,7 +10368,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="5"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>鈴木　聡</v>
               </pt>
@@ -10335,12 +10383,15 @@
               </pt>
               <pt idx="4">
                 <v>石澤　直道</v>
+              </pt>
+              <pt idx="5">
+                <v>伊勢　浩治</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="5"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -10354,6 +10405,9 @@
                 <v>0</v>
               </pt>
               <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
                 <v>0</v>
               </pt>
             </numLit>
@@ -10647,7 +10701,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="5"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>鈴木　聡</v>
               </pt>
@@ -10662,12 +10716,15 @@
               </pt>
               <pt idx="4">
                 <v>石澤　直道</v>
+              </pt>
+              <pt idx="5">
+                <v>伊勢　浩治</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="5"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -10681,6 +10738,9 @@
                 <v>0</v>
               </pt>
               <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
                 <v>0</v>
               </pt>
             </numLit>
@@ -10861,7 +10921,7 @@
                 <v>1</v>
               </pt>
               <pt idx="8">
-                <v>3</v>
+                <v>4</v>
               </pt>
             </numLit>
           </val>
@@ -13150,7 +13210,7 @@
         <v>0</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
@@ -13228,7 +13288,7 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>0</v>
@@ -13262,7 +13322,7 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>0</v>
@@ -13354,7 +13414,7 @@
         <v>1</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -13547,7 +13607,7 @@
         <v>2</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" s="4" t="n">
         <v>0</v>
@@ -13603,7 +13663,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O6" s="4" t="n">
         <v>0</v>
@@ -13622,7 +13682,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="4" t="n">
         <v>2</v>
@@ -13650,7 +13710,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="4" t="n">
         <v>1</v>
@@ -13746,7 +13806,7 @@
         <v>2</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -14296,7 +14356,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
@@ -14731,7 +14791,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>0</v>
@@ -14808,7 +14868,7 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>0</v>
@@ -14843,7 +14903,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>0</v>
@@ -14859,7 +14919,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>0</v>
@@ -14879,7 +14939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42.48" customWidth="1" min="1" max="1"/>
@@ -14893,6 +14953,7 @@
     <col width="9" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -14948,6 +15009,14 @@
 道</t>
         </is>
       </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>伊
+勢
+浩
+治</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
@@ -14970,6 +15039,9 @@
       <c r="M4" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="N4" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
@@ -14992,6 +15064,9 @@
       <c r="M5" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="N5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
@@ -15014,6 +15089,9 @@
       <c r="M6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
@@ -15036,6 +15114,9 @@
       <c r="M7" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="N7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
@@ -15058,6 +15139,9 @@
       <c r="M8" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="N8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="H9" s="4" t="inlineStr">
@@ -15080,6 +15164,9 @@
       <c r="M9" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="N9" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="H10" s="4" t="inlineStr">
@@ -15102,6 +15189,9 @@
       <c r="M10" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="N10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="H11" s="4" t="inlineStr">
@@ -15119,10 +15209,13 @@
         <v>0</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -15146,6 +15239,9 @@
       <c r="M12" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="N12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="H13" s="4" t="inlineStr">
@@ -15166,6 +15262,9 @@
         <v>0</v>
       </c>
       <c r="M13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/重点商品CA別進捗_2026年9月.xlsx
+++ b/重点商品CA別進捗_2026年9月.xlsx
@@ -436,7 +436,7 @@
                 <v>1</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -1450,7 +1450,7 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -2119,7 +2119,7 @@
             <numLit>
               <ptCount val="9"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -2128,7 +2128,7 @@
                 <v>2</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -3121,7 +3121,7 @@
                 <v>2</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -3598,7 +3598,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="3">
                 <v>2</v>
@@ -4711,7 +4711,7 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>1</v>
+                <v>2</v>
               </pt>
             </numLit>
           </val>
@@ -5311,7 +5311,7 @@
                 <v>2</v>
               </pt>
               <pt idx="3">
-                <v>1</v>
+                <v>2</v>
               </pt>
             </numLit>
           </val>
@@ -5617,7 +5617,7 @@
             <numLit>
               <ptCount val="9"/>
               <pt idx="0">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="1">
                 <v>2</v>
@@ -5626,7 +5626,7 @@
                 <v>2</v>
               </pt>
               <pt idx="3">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -5687,7 +5687,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6937,7 +6937,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>9</v>
+                <v>10</v>
               </pt>
               <pt idx="1">
                 <v>8</v>
@@ -6989,7 +6989,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="9"/>
+          <max val="10"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7243,7 +7243,7 @@
             <numLit>
               <ptCount val="9"/>
               <pt idx="0">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -7252,7 +7252,7 @@
                 <v>10</v>
               </pt>
               <pt idx="3">
-                <v>4</v>
+                <v>5</v>
               </pt>
               <pt idx="4">
                 <v>1</v>
@@ -7552,7 +7552,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -7693,7 +7693,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>2</v>
@@ -8128,7 +8128,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -8272,7 +8272,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="2">
                 <v>1</v>
@@ -8560,7 +8560,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -8863,7 +8863,7 @@
             <numLit>
               <ptCount val="9"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -10897,16 +10897,16 @@
             <numLit>
               <ptCount val="9"/>
               <pt idx="0">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="1">
                 <v>2</v>
               </pt>
               <pt idx="2">
-                <v>10</v>
+                <v>11</v>
               </pt>
               <pt idx="3">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -10967,7 +10967,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="10"/>
+          <max val="11"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -11086,7 +11086,7 @@
                 <v>1</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
@@ -13195,7 +13195,7 @@
         <v>2</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="4" t="n">
         <v>0</v>
@@ -13254,7 +13254,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>2</v>
@@ -13263,7 +13263,7 @@
         <v>2</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M7" s="4" t="n">
         <v>0</v>
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>0</v>
@@ -13297,7 +13297,7 @@
         <v>10</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>1</v>
@@ -13322,7 +13322,7 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>0</v>
@@ -13390,16 +13390,16 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>0</v>
@@ -13433,7 +13433,7 @@
         <v>1</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="4" t="n">
         <v>0</v>
@@ -13467,7 +13467,7 @@
         <v>1</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="4" t="n">
         <v>0</v>
@@ -13741,7 +13741,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M9" s="4" t="n">
         <v>0</v>
@@ -14079,7 +14079,7 @@
         <v>2</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -14145,7 +14145,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>2</v>
@@ -14356,7 +14356,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
@@ -14432,7 +14432,7 @@
         <v>2</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -14658,7 +14658,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>8</v>
@@ -14775,7 +14775,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>0</v>
@@ -14788,7 +14788,7 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>2</v>
@@ -14839,7 +14839,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>0</v>
@@ -14855,7 +14855,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>1</v>
@@ -14887,7 +14887,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>0</v>

--- a/重点商品CA別進捗_2026年9月.xlsx
+++ b/重点商品CA別進捗_2026年9月.xlsx
@@ -616,7 +616,7 @@
                 <v>2</v>
               </pt>
               <pt idx="5">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="6">
                 <v>0</v>
@@ -1792,7 +1792,7 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="6">
                 <v>1</v>
@@ -2626,7 +2626,7 @@
                 <v>1</v>
               </pt>
               <pt idx="2">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -2950,7 +2950,7 @@
                 <v>1</v>
               </pt>
               <pt idx="2">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -3274,7 +3274,7 @@
                 <v>1</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="3">
                 <v>1</v>
@@ -3592,7 +3592,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -6361,7 +6361,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>6</v>
+                <v>7</v>
               </pt>
               <pt idx="1">
                 <v>3</v>
@@ -6413,7 +6413,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="6"/>
+          <max val="7"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6937,7 +6937,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>10</v>
+                <v>11</v>
               </pt>
               <pt idx="1">
                 <v>8</v>
@@ -6989,7 +6989,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="10"/>
+          <max val="11"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7249,13 +7249,13 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>10</v>
+                <v>11</v>
               </pt>
               <pt idx="3">
-                <v>5</v>
+                <v>6</v>
               </pt>
               <pt idx="4">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="5">
                 <v>1</v>
@@ -7313,7 +7313,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="10"/>
+          <max val="11"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7405,7 +7405,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -8560,7 +8560,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -8609,7 +8609,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8875,7 +8875,7 @@
                 <v>0</v>
               </pt>
               <pt idx="4">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="5">
                 <v>2</v>
@@ -10903,10 +10903,10 @@
                 <v>2</v>
               </pt>
               <pt idx="2">
-                <v>11</v>
+                <v>13</v>
               </pt>
               <pt idx="3">
-                <v>4</v>
+                <v>5</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -10915,7 +10915,7 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="7">
                 <v>1</v>
@@ -10967,7 +10967,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="11"/>
+          <max val="13"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -13294,13 +13294,13 @@
         <v>0</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>1</v>
@@ -13334,7 +13334,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>2</v>
@@ -13396,10 +13396,10 @@
         <v>2</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>0</v>
@@ -13408,7 +13408,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P11" s="4" t="n">
         <v>1</v>
@@ -13607,7 +13607,7 @@
         <v>2</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O4" s="4" t="n">
         <v>0</v>
@@ -13803,7 +13803,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O11" s="4" t="n">
         <v>1</v>
@@ -13995,7 +13995,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>0</v>
@@ -14045,7 +14045,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" s="4" t="n">
         <v>0</v>
@@ -14095,7 +14095,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="4" t="n">
         <v>1</v>
@@ -14139,7 +14139,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>0</v>
@@ -14594,7 +14594,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>3</v>
@@ -14658,7 +14658,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>8</v>
@@ -14690,7 +14690,7 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>0</v>
@@ -14887,7 +14887,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>0</v>

--- a/重点商品CA別進捗_2026年9月.xlsx
+++ b/重点商品CA別進捗_2026年9月.xlsx
@@ -253,7 +253,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -317,7 +317,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -2125,7 +2125,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>2</v>
+                <v>4</v>
               </pt>
               <pt idx="3">
                 <v>1</v>
@@ -2189,7 +2189,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="4"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -2620,7 +2620,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>5</v>
+                <v>6</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -2681,7 +2681,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="5"/>
+          <max val="6"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -2944,7 +2944,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>5</v>
+                <v>6</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -3005,7 +3005,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="5"/>
+          <max val="6"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -3430,7 +3430,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -3592,7 +3592,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -3931,7 +3931,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -4702,7 +4702,7 @@
             <numLit>
               <ptCount val="4"/>
               <pt idx="0">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -4757,7 +4757,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="4"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -5302,7 +5302,7 @@
             <numLit>
               <ptCount val="4"/>
               <pt idx="0">
-                <v>4</v>
+                <v>5</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -5357,7 +5357,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="4"/>
+          <max val="5"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -5620,10 +5620,10 @@
                 <v>3</v>
               </pt>
               <pt idx="1">
-                <v>2</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="3">
                 <v>2</v>
@@ -6364,7 +6364,7 @@
                 <v>7</v>
               </pt>
               <pt idx="1">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -6793,10 +6793,10 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="1">
-                <v>5</v>
+                <v>6</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -6845,7 +6845,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="5"/>
+          <max val="6"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6937,10 +6937,10 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>11</v>
+                <v>14</v>
               </pt>
               <pt idx="1">
-                <v>8</v>
+                <v>9</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -6989,7 +6989,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="11"/>
+          <max val="14"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7249,7 +7249,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>11</v>
+                <v>12</v>
               </pt>
               <pt idx="3">
                 <v>6</v>
@@ -7313,7 +7313,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="11"/>
+          <max val="12"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8413,7 +8413,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>3</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -8465,7 +8465,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8881,7 +8881,7 @@
                 <v>2</v>
               </pt>
               <pt idx="6">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="7">
                 <v>0</v>
@@ -13158,7 +13158,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4" s="4" t="n">
         <v>0</v>
@@ -13192,7 +13192,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>1</v>
@@ -13226,7 +13226,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="4" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>3</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L7" s="4" t="n">
         <v>2</v>
@@ -13294,7 +13294,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L8" s="4" t="n">
         <v>6</v>
@@ -13340,7 +13340,7 @@
         <v>2</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P9" s="4" t="n">
         <v>0</v>
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>1</v>
@@ -14039,7 +14039,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>1</v>
@@ -14114,7 +14114,7 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>0</v>
@@ -14139,7 +14139,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>0</v>
@@ -14347,7 +14347,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>1</v>
@@ -14423,7 +14423,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>0</v>
@@ -14597,7 +14597,7 @@
         <v>7</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>0</v>
@@ -14642,10 +14642,10 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>0</v>
@@ -14658,10 +14658,10 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>0</v>
@@ -14868,7 +14868,7 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>0</v>

--- a/重点商品CA別進捗_2026年9月.xlsx
+++ b/重点商品CA別進捗_2026年9月.xlsx
@@ -256,10 +256,10 @@
                 <v>3</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="4">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="5">
                 <v>0</v>
@@ -946,7 +946,7 @@
                 <v>1</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -1453,7 +1453,7 @@
                 <v>3</v>
               </pt>
               <pt idx="4">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="5">
                 <v>1</v>
@@ -1783,10 +1783,10 @@
                 <v>4</v>
               </pt>
               <pt idx="2">
-                <v>4</v>
+                <v>5</v>
               </pt>
               <pt idx="3">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -1841,7 +1841,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="4"/>
+          <max val="5"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -2950,7 +2950,7 @@
                 <v>1</v>
               </pt>
               <pt idx="2">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -3274,7 +3274,7 @@
                 <v>1</v>
               </pt>
               <pt idx="2">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="3">
                 <v>1</v>
@@ -3607,7 +3607,7 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>2</v>
+                <v>3</v>
               </pt>
             </numLit>
           </val>
@@ -5305,7 +5305,7 @@
                 <v>5</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>3</v>
               </pt>
               <pt idx="2">
                 <v>2</v>
@@ -6073,7 +6073,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -6361,7 +6361,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>7</v>
+                <v>9</v>
               </pt>
               <pt idx="1">
                 <v>4</v>
@@ -6413,7 +6413,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="7"/>
+          <max val="9"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6793,7 +6793,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>4</v>
+                <v>5</v>
               </pt>
               <pt idx="1">
                 <v>6</v>
@@ -6937,7 +6937,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>14</v>
+                <v>17</v>
               </pt>
               <pt idx="1">
                 <v>9</v>
@@ -6989,7 +6989,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="14"/>
+          <max val="17"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7243,7 +7243,7 @@
             <numLit>
               <ptCount val="9"/>
               <pt idx="0">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -7252,7 +7252,7 @@
                 <v>12</v>
               </pt>
               <pt idx="3">
-                <v>6</v>
+                <v>8</v>
               </pt>
               <pt idx="4">
                 <v>2</v>
@@ -7267,7 +7267,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>2</v>
+                <v>3</v>
               </pt>
             </numLit>
           </val>
@@ -8269,7 +8269,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>2</v>
@@ -8869,7 +8869,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>6</v>
+                <v>7</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -10906,7 +10906,7 @@
                 <v>13</v>
               </pt>
               <pt idx="3">
-                <v>5</v>
+                <v>7</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -13161,10 +13161,10 @@
         <v>3</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" s="4" t="n">
         <v>0</v>
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>0</v>
@@ -13297,7 +13297,7 @@
         <v>12</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>2</v>
@@ -13312,7 +13312,7 @@
         <v>0</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -13328,7 +13328,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L9" s="4" t="n">
         <v>0</v>
@@ -13399,7 +13399,7 @@
         <v>13</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>0</v>
@@ -13657,7 +13657,7 @@
         <v>1</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="4" t="n">
         <v>0</v>
@@ -13744,7 +13744,7 @@
         <v>3</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>1</v>
@@ -13794,10 +13794,10 @@
         <v>4</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>0</v>
@@ -14045,7 +14045,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L7" s="4" t="n">
         <v>0</v>
@@ -14095,7 +14095,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" s="4" t="n">
         <v>1</v>
@@ -14154,7 +14154,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -14426,7 +14426,7 @@
         <v>5</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>2</v>
@@ -14562,7 +14562,7 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
@@ -14594,7 +14594,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>4</v>
@@ -14642,7 +14642,7 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>6</v>
@@ -14658,7 +14658,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>9</v>
@@ -14852,7 +14852,7 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>2</v>

--- a/重点商品CA別進捗_2026年9月.xlsx
+++ b/重点商品CA別進捗_2026年9月.xlsx
@@ -784,7 +784,7 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="6">
                 <v>1</v>
@@ -946,13 +946,13 @@
                 <v>1</v>
               </pt>
               <pt idx="3">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="6">
                 <v>0</v>
@@ -1001,7 +1001,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -1792,7 +1792,7 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="6">
                 <v>1</v>
@@ -1954,13 +1954,13 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="6">
                 <v>0</v>
@@ -4558,7 +4558,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -5002,7 +5002,7 @@
             <numLit>
               <ptCount val="4"/>
               <pt idx="0">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="1">
                 <v>2</v>
@@ -5308,7 +5308,7 @@
                 <v>3</v>
               </pt>
               <pt idx="2">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="3">
                 <v>2</v>
@@ -7549,7 +7549,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -7981,7 +7981,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -8557,7 +8557,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>0</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>3</v>
@@ -8701,7 +8701,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -8753,7 +8753,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -9025,7 +9025,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -10897,7 +10897,7 @@
             <numLit>
               <ptCount val="9"/>
               <pt idx="0">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="1">
                 <v>2</v>
@@ -13390,7 +13390,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>2</v>
@@ -13635,7 +13635,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>1</v>
@@ -13657,13 +13657,13 @@
         <v>1</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O6" s="4" t="n">
         <v>0</v>
@@ -13803,7 +13803,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O11" s="4" t="n">
         <v>1</v>
@@ -13825,13 +13825,13 @@
         <v>0</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" s="4" t="n">
         <v>0</v>
@@ -14334,7 +14334,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="4" t="n">
         <v>0</v>
@@ -14385,7 +14385,7 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>2</v>
@@ -14429,7 +14429,7 @@
         <v>3</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>2</v>
@@ -14772,7 +14772,7 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>1</v>
@@ -14820,7 +14820,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>0</v>
@@ -14884,7 +14884,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>3</v>
@@ -14900,7 +14900,7 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>1</v>
@@ -14916,7 +14916,7 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>1</v>

--- a/重点商品CA別進捗_2026年9月.xlsx
+++ b/重点商品CA別進捗_2026年9月.xlsx
@@ -619,7 +619,7 @@
                 <v>2</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -955,7 +955,7 @@
                 <v>3</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -1123,7 +1123,7 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>1</v>
+                <v>2</v>
               </pt>
             </numLit>
           </val>
@@ -1450,7 +1450,7 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="4">
                 <v>1</v>
@@ -1795,7 +1795,7 @@
                 <v>4</v>
               </pt>
               <pt idx="6">
-                <v>1</v>
+                <v>2</v>
               </pt>
             </numLit>
           </val>
@@ -2470,7 +2470,7 @@
                 <v>0</v>
               </pt>
               <pt idx="4">
-                <v>3</v>
+                <v>5</v>
               </pt>
               <pt idx="5">
                 <v>0</v>
@@ -2632,7 +2632,7 @@
                 <v>0</v>
               </pt>
               <pt idx="4">
-                <v>3</v>
+                <v>5</v>
               </pt>
               <pt idx="5">
                 <v>0</v>
@@ -2956,7 +2956,7 @@
                 <v>0</v>
               </pt>
               <pt idx="4">
-                <v>3</v>
+                <v>5</v>
               </pt>
               <pt idx="5">
                 <v>0</v>
@@ -3118,7 +3118,7 @@
                 <v>0</v>
               </pt>
               <pt idx="4">
-                <v>2</v>
+                <v>4</v>
               </pt>
               <pt idx="5">
                 <v>1</v>
@@ -3280,7 +3280,7 @@
                 <v>1</v>
               </pt>
               <pt idx="4">
-                <v>3</v>
+                <v>5</v>
               </pt>
               <pt idx="5">
                 <v>0</v>
@@ -4711,7 +4711,7 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>2</v>
+                <v>3</v>
               </pt>
             </numLit>
           </val>
@@ -5308,7 +5308,7 @@
                 <v>3</v>
               </pt>
               <pt idx="2">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="3">
                 <v>2</v>
@@ -6361,7 +6361,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>9</v>
+                <v>10</v>
               </pt>
               <pt idx="1">
                 <v>4</v>
@@ -6413,7 +6413,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="9"/>
+          <max val="10"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6649,7 +6649,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="1">
                 <v>3</v>
@@ -6937,7 +6937,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>17</v>
+                <v>18</v>
               </pt>
               <pt idx="1">
                 <v>9</v>
@@ -6989,7 +6989,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="17"/>
+          <max val="18"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7252,7 +7252,7 @@
                 <v>12</v>
               </pt>
               <pt idx="3">
-                <v>8</v>
+                <v>11</v>
               </pt>
               <pt idx="4">
                 <v>2</v>
@@ -9172,7 +9172,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -9478,7 +9478,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -10243,7 +10243,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -10301,7 +10301,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -10897,7 +10897,7 @@
             <numLit>
               <ptCount val="9"/>
               <pt idx="0">
-                <v>4</v>
+                <v>5</v>
               </pt>
               <pt idx="1">
                 <v>2</v>
@@ -10906,10 +10906,10 @@
                 <v>13</v>
               </pt>
               <pt idx="3">
-                <v>7</v>
+                <v>10</v>
               </pt>
               <pt idx="4">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="5">
                 <v>0</v>
@@ -13297,7 +13297,7 @@
         <v>12</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>2</v>
@@ -13390,7 +13390,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>2</v>
@@ -13399,10 +13399,10 @@
         <v>13</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -13610,7 +13610,7 @@
         <v>2</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="358.5826771653543" customHeight="1">
@@ -13666,7 +13666,7 @@
         <v>3</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -13694,7 +13694,7 @@
         <v>0</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
@@ -13741,7 +13741,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M9" s="4" t="n">
         <v>1</v>
@@ -13806,7 +13806,7 @@
         <v>4</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -13976,7 +13976,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N4" s="4" t="n">
         <v>0</v>
@@ -14001,7 +14001,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
@@ -14051,7 +14051,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
@@ -14076,7 +14076,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>1</v>
@@ -14101,7 +14101,7 @@
         <v>1</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
@@ -14356,7 +14356,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
@@ -14429,7 +14429,7 @@
         <v>3</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>2</v>
@@ -14594,7 +14594,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>4</v>
@@ -14626,7 +14626,7 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>3</v>
@@ -14658,7 +14658,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>9</v>
@@ -15028,7 +15028,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>0</v>
@@ -15078,7 +15078,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>0</v>
@@ -15203,7 +15203,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>0</v>

--- a/重点商品CA別進捗_2026年9月.xlsx
+++ b/重点商品CA別進捗_2026年9月.xlsx
@@ -1453,7 +1453,7 @@
                 <v>4</v>
               </pt>
               <pt idx="4">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="5">
                 <v>1</v>
@@ -3595,10 +3595,10 @@
                 <v>3</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
-                <v>2</v>
+                <v>4</v>
               </pt>
               <pt idx="3">
                 <v>2</v>
@@ -3653,7 +3653,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="4"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -3934,7 +3934,7 @@
                 <v>2</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -5626,7 +5626,7 @@
                 <v>3</v>
               </pt>
               <pt idx="3">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -5929,7 +5929,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -6217,7 +6217,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -6361,7 +6361,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>10</v>
+                <v>11</v>
               </pt>
               <pt idx="1">
                 <v>4</v>
@@ -6413,7 +6413,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="10"/>
+          <max val="11"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6505,7 +6505,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -6937,7 +6937,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>18</v>
+                <v>19</v>
               </pt>
               <pt idx="1">
                 <v>9</v>
@@ -6989,7 +6989,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="18"/>
+          <max val="19"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7252,7 +7252,7 @@
                 <v>12</v>
               </pt>
               <pt idx="3">
-                <v>11</v>
+                <v>14</v>
               </pt>
               <pt idx="4">
                 <v>2</v>
@@ -7313,7 +7313,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="12"/>
+          <max val="14"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8272,7 +8272,7 @@
                 <v>1</v>
               </pt>
               <pt idx="1">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="2">
                 <v>1</v>
@@ -8560,7 +8560,7 @@
                 <v>2</v>
               </pt>
               <pt idx="1">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -8609,7 +8609,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="4"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -10906,7 +10906,7 @@
                 <v>13</v>
               </pt>
               <pt idx="3">
-                <v>10</v>
+                <v>13</v>
               </pt>
               <pt idx="4">
                 <v>1</v>
@@ -10915,7 +10915,7 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="7">
                 <v>1</v>
@@ -13229,7 +13229,7 @@
         <v>2</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="4" t="n">
         <v>0</v>
@@ -13263,7 +13263,7 @@
         <v>3</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M7" s="4" t="n">
         <v>0</v>
@@ -13297,7 +13297,7 @@
         <v>12</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>2</v>
@@ -13399,7 +13399,7 @@
         <v>13</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>1</v>
@@ -13408,7 +13408,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P11" s="4" t="n">
         <v>1</v>
@@ -13744,7 +13744,7 @@
         <v>4</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>1</v>
@@ -14142,10 +14142,10 @@
         <v>3</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>2</v>
@@ -14546,7 +14546,7 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>0</v>
@@ -14578,7 +14578,7 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>0</v>
@@ -14594,7 +14594,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>4</v>
@@ -14610,7 +14610,7 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>0</v>
@@ -14658,7 +14658,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>9</v>
@@ -14855,7 +14855,7 @@
         <v>1</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>1</v>
@@ -14887,7 +14887,7 @@
         <v>2</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>0</v>

--- a/重点商品CA別進捗_2026年9月.xlsx
+++ b/重点商品CA別進捗_2026年9月.xlsx
@@ -271,7 +271,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -604,7 +604,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -619,7 +619,7 @@
                 <v>2</v>
               </pt>
               <pt idx="6">
-                <v>1</v>
+                <v>2</v>
               </pt>
             </numLit>
           </val>
@@ -1453,7 +1453,7 @@
                 <v>4</v>
               </pt>
               <pt idx="4">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="5">
                 <v>1</v>
@@ -1792,7 +1792,7 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>4</v>
+                <v>5</v>
               </pt>
               <pt idx="6">
                 <v>2</v>
@@ -2296,7 +2296,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -2464,7 +2464,7 @@
                 <v>1</v>
               </pt>
               <pt idx="2">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -2473,7 +2473,7 @@
                 <v>5</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -2626,7 +2626,7 @@
                 <v>1</v>
               </pt>
               <pt idx="2">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -2950,7 +2950,7 @@
                 <v>1</v>
               </pt>
               <pt idx="2">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -2959,7 +2959,7 @@
                 <v>5</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -3109,10 +3109,10 @@
                 <v>4</v>
               </pt>
               <pt idx="1">
+                <v>2</v>
+              </pt>
+              <pt idx="2">
                 <v>1</v>
-              </pt>
-              <pt idx="2">
-                <v>0</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -3121,7 +3121,7 @@
                 <v>4</v>
               </pt>
               <pt idx="5">
-                <v>1</v>
+                <v>2</v>
               </pt>
             </numLit>
           </val>
@@ -3274,7 +3274,7 @@
                 <v>1</v>
               </pt>
               <pt idx="2">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="3">
                 <v>1</v>
@@ -3601,10 +3601,10 @@
                 <v>4</v>
               </pt>
               <pt idx="3">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="4">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="5">
                 <v>3</v>
@@ -3757,7 +3757,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -4705,7 +4705,7 @@
                 <v>4</v>
               </pt>
               <pt idx="1">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -4861,7 +4861,7 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -5005,7 +5005,7 @@
                 <v>3</v>
               </pt>
               <pt idx="1">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -5305,7 +5305,7 @@
                 <v>5</v>
               </pt>
               <pt idx="1">
-                <v>3</v>
+                <v>5</v>
               </pt>
               <pt idx="2">
                 <v>4</v>
@@ -5641,7 +5641,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>2</v>
+                <v>3</v>
               </pt>
             </numLit>
           </val>
@@ -5785,7 +5785,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -5837,7 +5837,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6937,7 +6937,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>19</v>
+                <v>20</v>
               </pt>
               <pt idx="1">
                 <v>9</v>
@@ -6989,7 +6989,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="19"/>
+          <max val="20"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7252,7 +7252,7 @@
                 <v>12</v>
               </pt>
               <pt idx="3">
-                <v>14</v>
+                <v>15</v>
               </pt>
               <pt idx="4">
                 <v>2</v>
@@ -7267,7 +7267,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>3</v>
+                <v>5</v>
               </pt>
             </numLit>
           </val>
@@ -7313,7 +7313,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="14"/>
+          <max val="15"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7981,10 +7981,10 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
+                <v>2</v>
+              </pt>
+              <pt idx="1">
                 <v>1</v>
-              </pt>
-              <pt idx="1">
-                <v>0</v>
               </pt>
               <pt idx="2">
                 <v>1</v>
@@ -8033,7 +8033,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8413,10 +8413,10 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -8465,7 +8465,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8557,10 +8557,10 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>2</v>
+                <v>4</v>
               </pt>
               <pt idx="1">
-                <v>4</v>
+                <v>5</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -8609,7 +8609,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="4"/>
+          <max val="5"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8881,13 +8881,13 @@
                 <v>2</v>
               </pt>
               <pt idx="6">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="7">
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -10249,7 +10249,7 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="4">
                 <v>1</v>
@@ -10897,16 +10897,16 @@
             <numLit>
               <ptCount val="9"/>
               <pt idx="0">
-                <v>5</v>
+                <v>8</v>
               </pt>
               <pt idx="1">
-                <v>2</v>
+                <v>4</v>
               </pt>
               <pt idx="2">
                 <v>13</v>
               </pt>
               <pt idx="3">
-                <v>13</v>
+                <v>16</v>
               </pt>
               <pt idx="4">
                 <v>1</v>
@@ -10921,7 +10921,7 @@
                 <v>1</v>
               </pt>
               <pt idx="8">
-                <v>4</v>
+                <v>5</v>
               </pt>
             </numLit>
           </val>
@@ -10967,7 +10967,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="13"/>
+          <max val="16"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -13176,7 +13176,7 @@
         <v>0</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="358.5826771653543" customHeight="1">
@@ -13278,7 +13278,7 @@
         <v>0</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
@@ -13297,7 +13297,7 @@
         <v>12</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>2</v>
@@ -13312,7 +13312,7 @@
         <v>0</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -13340,13 +13340,13 @@
         <v>2</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -13390,16 +13390,16 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>13</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>1</v>
@@ -13414,7 +13414,7 @@
         <v>1</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -13595,7 +13595,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>0</v>
@@ -13610,7 +13610,7 @@
         <v>2</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" ht="358.5826771653543" customHeight="1">
@@ -13744,7 +13744,7 @@
         <v>4</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>1</v>
@@ -13803,7 +13803,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O11" s="4" t="n">
         <v>2</v>
@@ -13847,7 +13847,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>0</v>
@@ -13970,7 +13970,7 @@
         <v>1</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" s="4" t="n">
         <v>0</v>
@@ -13979,7 +13979,7 @@
         <v>5</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="358.5826771653543" customHeight="1">
@@ -13995,7 +13995,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>0</v>
@@ -14045,7 +14045,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L7" s="4" t="n">
         <v>0</v>
@@ -14054,7 +14054,7 @@
         <v>5</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
@@ -14067,10 +14067,10 @@
         <v>4</v>
       </c>
       <c r="J8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="L8" s="4" t="n">
         <v>0</v>
@@ -14079,7 +14079,7 @@
         <v>4</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -14095,7 +14095,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L9" s="4" t="n">
         <v>1</v>
@@ -14148,10 +14148,10 @@
         <v>4</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>3</v>
@@ -14167,7 +14167,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>0</v>
@@ -14350,7 +14350,7 @@
         <v>4</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>0</v>
@@ -14375,7 +14375,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -14388,7 +14388,7 @@
         <v>3</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>0</v>
@@ -14426,7 +14426,7 @@
         <v>5</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>4</v>
@@ -14464,7 +14464,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>0</v>
@@ -14658,7 +14658,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>9</v>
@@ -14820,10 +14820,10 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>1</v>
@@ -14868,10 +14868,10 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>0</v>
@@ -14884,10 +14884,10 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>0</v>
@@ -15209,7 +15209,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>1</v>
